--- a/internal_doc/05.测试设计/可靠性测试/主子表故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/主子表故障测试设计_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$143</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -683,7 +683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C81" authorId="0">
+    <comment ref="E81" authorId="0">
       <text>
         <r>
           <rPr>
@@ -709,7 +709,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C83" authorId="0">
+    <comment ref="E83" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1162,7 +1162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E142" authorId="0">
+    <comment ref="E141" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1188,7 +1188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A145" authorId="0">
+    <comment ref="A144" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1253,7 +1253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C149" authorId="0">
+    <comment ref="C148" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1284,7 +1284,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="157">
   <si>
     <t>dataRG主节点所在服务器CPU耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1856,10 +1856,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同断网，另考虑coord、catalog、dataRG组合的场景，如下：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>catalog主节点跟其他catalog备节点网络单通</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1893,11 +1889,6 @@
   </si>
   <si>
     <t>网络拥塞达到选主条件时重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert/upsert/remove
-两个分区组各挂载一个子表，在同一个coord操作，其中一个分区组不停挂载和分离子表，另外一个做基本操作，测试编目信息旧的情况</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1920,6 +1911,46 @@
   <si>
     <t>dataRG主节点与dataRG备节点网络单通
 （数据节点网络单通情况放在基本操作里面测试（余婷））</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attachCL/detachCL/基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同断网，另考虑coord、catalog、dataRG组合的场景，如下：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点目录所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点目录所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点目录所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点目录所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点目录所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点目录所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点目录所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点目录所在盘umount（基本操作考虑（余婷））</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2068,7 +2099,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2113,6 +2144,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2414,7 +2448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2592,7 +2626,7 @@
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>59</v>
@@ -2663,7 +2697,7 @@
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>66</v>
@@ -2706,7 +2740,7 @@
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>70</v>
@@ -2736,7 +2770,7 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>73</v>
@@ -3035,7 +3069,7 @@
         <v>78</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>79</v>
@@ -3348,7 +3382,7 @@
         <v>85</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>0</v>
@@ -3523,10 +3557,12 @@
         <v>48</v>
       </c>
       <c r="C81" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
       <c r="F81" s="4" t="s">
         <v>25</v>
       </c>
@@ -3537,11 +3573,11 @@
     <row r="82" spans="1:7" ht="27">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
         <v>25</v>
       </c>
@@ -3550,24 +3586,24 @@
     <row r="83" spans="1:7" ht="27">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
         <v>101</v>
       </c>
       <c r="G83" s="7"/>
     </row>
-    <row r="84" spans="1:7" ht="40.5">
+    <row r="84" spans="1:7" ht="27">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
         <v>26</v>
       </c>
@@ -3611,7 +3647,7 @@
       <c r="C87" s="8"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -4156,7 +4192,7 @@
         <v>48</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -4209,7 +4245,7 @@
       <c r="B134" s="7"/>
       <c r="C134" s="8"/>
       <c r="D134" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>130</v>
@@ -4276,11 +4312,13 @@
       </c>
       <c r="C139" s="5"/>
       <c r="D139" s="4"/>
-      <c r="E139" s="4"/>
+      <c r="E139" s="16" t="s">
+        <v>148</v>
+      </c>
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
     </row>
-    <row r="140" spans="1:7" ht="40.5">
+    <row r="140" spans="1:7" ht="27">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -4288,19 +4326,21 @@
       <c r="E140" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F140" s="7"/>
+      <c r="F140" s="7" t="s">
+        <v>136</v>
+      </c>
       <c r="G140" s="7"/>
     </row>
-    <row r="141" spans="1:7" ht="27">
+    <row r="141" spans="1:7" ht="67.5">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
-      <c r="E141" s="7" t="s">
-        <v>134</v>
+      <c r="E141" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="G141" s="7"/>
     </row>
@@ -4310,91 +4350,93 @@
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="G142" s="7"/>
     </row>
-    <row r="143" spans="1:7" ht="67.5">
+    <row r="143" spans="1:7" ht="27">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
-      <c r="E143" s="10" t="s">
-        <v>148</v>
+      <c r="E143" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G143" s="7"/>
     </row>
-    <row r="144" spans="1:7" ht="27">
-      <c r="A144" s="7"/>
-      <c r="B144" s="7"/>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G144" s="7"/>
-    </row>
-    <row r="145" spans="1:7" ht="40.5">
-      <c r="A145" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B145" s="4" t="s">
+    <row r="144" spans="1:7" ht="40.5">
+      <c r="A144" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B144" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="C144" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D145" s="4"/>
-      <c r="E145" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F145" s="4" t="s">
+      <c r="D144" s="4"/>
+      <c r="E144" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F144" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G145" s="4"/>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="G144" s="4"/>
+    </row>
+    <row r="145" spans="1:7" ht="27">
+      <c r="A145" s="7"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G145" s="7"/>
+    </row>
+    <row r="146" spans="1:7" ht="27">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="8"/>
+      <c r="C146" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="D146" s="7"/>
       <c r="E146" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F146" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="F146" s="7"/>
       <c r="G146" s="7"/>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" ht="27">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
-      <c r="C147" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="C147" s="8"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7" t="s">
-        <v>6</v>
+        <v>152</v>
       </c>
       <c r="F147" s="7"/>
       <c r="G147" s="7"/>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" ht="67.5">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
-      <c r="C148" s="8"/>
-      <c r="D148" s="7"/>
+      <c r="C148" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="E148" s="7" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
@@ -4402,71 +4444,65 @@
     <row r="149" spans="1:7" ht="67.5">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="8" t="s">
-        <v>85</v>
-      </c>
+      <c r="C149" s="8"/>
       <c r="D149" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
     </row>
-    <row r="150" spans="1:7" ht="67.5">
+    <row r="150" spans="1:7" ht="27">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
-      <c r="C150" s="8"/>
+      <c r="C150" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="D150" s="7" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F150" s="7"/>
       <c r="G150" s="7"/>
     </row>
-    <row r="151" spans="1:7" ht="27">
+    <row r="151" spans="1:7" ht="40.5">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>4</v>
+        <v>27</v>
+      </c>
+      <c r="D151" s="7"/>
+      <c r="E151" s="10" t="s">
+        <v>156</v>
       </c>
       <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
+      <c r="G151" s="10"/>
     </row>
     <row r="152" spans="1:7" ht="40.5">
-      <c r="A152" s="7"/>
-      <c r="B152" s="7"/>
-      <c r="C152" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D152" s="7"/>
-      <c r="E152" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F152" s="7"/>
-      <c r="G152" s="10"/>
-    </row>
-    <row r="153" spans="1:7" ht="40.5">
-      <c r="A153" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B153" s="4" t="s">
+      <c r="A152" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B152" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C153" s="5"/>
-      <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
-      <c r="F153" s="4"/>
-      <c r="G153" s="4"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="8"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="7"/>
@@ -4478,22 +4514,13 @@
       <c r="G154" s="7"/>
     </row>
     <row r="155" spans="1:7">
-      <c r="A155" s="7"/>
-      <c r="B155" s="7"/>
-      <c r="C155" s="8"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="D156" s="9"/>
-      <c r="E156" s="9"/>
-      <c r="F156" s="9"/>
-      <c r="G156" s="9"/>
+      <c r="D155" s="9"/>
+      <c r="E155" s="9"/>
+      <c r="F155" s="9"/>
+      <c r="G155" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G144"/>
+  <autoFilter ref="A1:G143"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/internal_doc/05.测试设计/可靠性测试/主子表故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/主子表故障测试设计_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$146</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -49,39 +49,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0">
+    <comment ref="E5" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Author:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>子表挂载必然成功，且能对主表进行基本操作</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
@@ -97,7 +71,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-不用测试</t>
+新增编目节点连续降备的情况</t>
         </r>
       </text>
     </comment>
@@ -108,6 +82,58 @@
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Author:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>子表挂载必然成功，且能对主表进行基本操作</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+不用测试</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
@@ -127,7 +153,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0">
+    <comment ref="C8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -172,7 +198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0">
+    <comment ref="E12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -198,7 +224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0">
+    <comment ref="F13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -224,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0">
+    <comment ref="E14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -250,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0">
+    <comment ref="D15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -276,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F15" authorId="0">
+    <comment ref="F16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -302,7 +328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C17" authorId="0">
+    <comment ref="C18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -337,7 +363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D17" authorId="0">
+    <comment ref="D18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -363,7 +389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C20" authorId="0">
+    <comment ref="C21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -398,7 +424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0">
+    <comment ref="F23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -432,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C23" authorId="0">
+    <comment ref="C24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -458,7 +484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E36" authorId="0">
+    <comment ref="E39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -483,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F44" authorId="0">
+    <comment ref="F47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E48" authorId="0">
+    <comment ref="E51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -535,7 +561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E55" authorId="0">
+    <comment ref="E58" authorId="0">
       <text>
         <r>
           <rPr>
@@ -561,7 +587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E69" authorId="0">
+    <comment ref="E72" authorId="0">
       <text>
         <r>
           <rPr>
@@ -596,7 +622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E75" authorId="0">
+    <comment ref="E78" authorId="0">
       <text>
         <r>
           <rPr>
@@ -631,7 +657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E77" authorId="0">
+    <comment ref="E80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -657,7 +683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E79" authorId="0">
+    <comment ref="E82" authorId="0">
       <text>
         <r>
           <rPr>
@@ -683,7 +709,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E81" authorId="0">
+    <comment ref="E84" authorId="0">
       <text>
         <r>
           <rPr>
@@ -709,7 +735,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E83" authorId="0">
+    <comment ref="E86" authorId="0">
       <text>
         <r>
           <rPr>
@@ -735,7 +761,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A85" authorId="0">
+    <comment ref="A88" authorId="0">
       <text>
         <r>
           <rPr>
@@ -769,7 +795,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E85" authorId="0">
+    <comment ref="E88" authorId="0">
       <text>
         <r>
           <rPr>
@@ -797,7 +823,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E96" authorId="0">
+    <comment ref="E99" authorId="0">
       <text>
         <r>
           <rPr>
@@ -823,7 +849,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C101" authorId="0">
+    <comment ref="C104" authorId="0">
       <text>
         <r>
           <rPr>
@@ -849,7 +875,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E102" authorId="0">
+    <comment ref="E105" authorId="0">
       <text>
         <r>
           <rPr>
@@ -875,7 +901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E107" authorId="0">
+    <comment ref="E110" authorId="0">
       <text>
         <r>
           <rPr>
@@ -901,7 +927,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A108" authorId="0">
+    <comment ref="A111" authorId="0">
       <text>
         <r>
           <rPr>
@@ -927,7 +953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C117" authorId="0">
+    <comment ref="C120" authorId="0">
       <text>
         <r>
           <rPr>
@@ -953,7 +979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E118" authorId="0">
+    <comment ref="E121" authorId="0">
       <text>
         <r>
           <rPr>
@@ -979,7 +1005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E123" authorId="0">
+    <comment ref="E126" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1002,32 +1028,6 @@
           </rPr>
           <t xml:space="preserve">
 基本操作考虑，这里不考虑</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A124" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-同上</t>
         </r>
       </text>
     </comment>
@@ -1079,11 +1079,37 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-等友滨确认后再考虑具体测试点</t>
+同上</t>
         </r>
       </text>
     </comment>
-    <comment ref="D133" authorId="0">
+    <comment ref="A133" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+等友滨确认后再考虑具体测试点</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D136" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1109,7 +1135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D137" authorId="0">
+    <comment ref="D140" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1135,7 +1161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A139" authorId="0">
+    <comment ref="A142" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1162,7 +1188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E141" authorId="0">
+    <comment ref="E144" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1188,7 +1214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A144" authorId="0">
+    <comment ref="A147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1253,7 +1279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C148" authorId="0">
+    <comment ref="C151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1284,7 +1310,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="166">
   <si>
     <t>dataRG主节点所在服务器CPU耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1313,12 +1339,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-  </si>
-  <si>
-    <t>断网后组内连续降备选主；恢复网络后查看是否从新的主节点同步数据；挂载成功在对应主表做基本操作成功(如insert数据)；主表catalog数据完整且一致；</t>
-  </si>
-  <si>
     <t>重启后组内重新选主；恢复后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
   </si>
   <si>
@@ -1430,10 +1450,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>闪断不超过选主的最小时间7s则不触发选主，attachCL成功，在主表做基本操作成功；闪断超过7s后组内重新选主，恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1487,29 +1503,6 @@
   </si>
   <si>
     <t>dataRG主节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG连续降备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>断网后组内连续降备选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <strike/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>挂载失败在该普通表做基本操作成功；</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1560,25 +1553,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>断网后组内连续降备选主；恢复网络后查看是否从新的主节点同步数据；insert成功，数据完整，可正常查询；</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <strike/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>insert失败数据丢失，不存在垃圾数据；</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在主表upsert大量数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1588,10 +1562,6 @@
   </si>
   <si>
     <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；upsert成功，数据被更新；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断网后组内连续降备选主；恢复网络后查看是否从新的主节点同步数据；upsert成功，数据被更新；upsert失败数据不被更新，数据正常存在；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1697,10 +1667,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>时间跳变后catalog数据不丢失，各节点数据完整一致；attachCL成功，对主表做基本操作，操作成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>时间跳变后catalog数据不丢失，各节点数据完整一致；detachCL成功，对普通表做基本操作，操作成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1951,6 +1917,68 @@
   </si>
   <si>
     <t>dataRG主节点目录所在盘umount（基本操作考虑（余婷））</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点连续降备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网后组内主节点连续降备选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+  </si>
+  <si>
+    <t>dataRG主节点连续降备</t>
+  </si>
+  <si>
+    <t>断网后组内主节点连续降备选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；挂载失败在该普通表做基本操作成功；</t>
+  </si>
+  <si>
+    <t>断网后组内主节点连续降备选主；恢复网络后查看是否从新的主节点同步数据；挂载成功在对应主表做基本操作成功(如insert数据)；主表catalog数据完整且一致；</t>
+  </si>
+  <si>
+    <t>断网后组内主节点连续降备选主；恢复网络后查看是否从新的主节点同步数据；insert成功，数据完整，可正常查询；insert失败数据丢失，不存在垃圾数据；</t>
+  </si>
+  <si>
+    <t>断网后组内主节点连续降备选主；恢复网络后查看是否从新的主节点同步数据；upsert成功，数据被更新；upsert失败数据不被更新，数据正常存在；</t>
+  </si>
+  <si>
+    <t>catalog主节点连续降备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点连续降备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detachCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪断不超过选主的最小时间7s则不触发选主，attachCL成功，在主表做基本操作成功；闪断超过7s后组内重新选主，恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变后catalog数据不丢失，各节点数据完整一致；attachCL成功，对主表做基本操作，操作成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2448,7 +2476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2463,43 +2491,43 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="27">
       <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="40.5">
       <c r="A2" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -2509,10 +2537,10 @@
       <c r="C3" s="8"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G3" s="7"/>
     </row>
@@ -2522,10 +2550,10 @@
       <c r="C4" s="8"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="7"/>
     </row>
@@ -2534,65 +2562,65 @@
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
-      <c r="E5" s="7" t="s">
-        <v>54</v>
+      <c r="E5" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="40.5">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7" ht="40.5">
+    <row r="7" spans="1:7">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="C7" s="8"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" ht="40.5">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" ht="40.5">
+    <row r="9" spans="1:7">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G9" s="7"/>
     </row>
@@ -2602,67 +2630,65 @@
       <c r="C10" s="8"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" ht="40.5">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" ht="40.5">
+    <row r="12" spans="1:7">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" ht="40.5">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="7"/>
+      <c r="C13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" ht="40.5">
+    <row r="14" spans="1:7">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="7"/>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="40.5">
@@ -2670,167 +2696,169 @@
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
       <c r="D15" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" ht="40.5">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="E16" s="7" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" ht="27">
+    <row r="17" spans="1:7">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" ht="27">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="7"/>
+      <c r="C18" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E18" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" ht="40.5">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>52</v>
+        <v>157</v>
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" spans="1:7" ht="40.5">
+    <row r="20" spans="1:7">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>70</v>
-      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="40.5">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="7"/>
+      <c r="C21" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="E21" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:7" ht="40.5">
+    <row r="22" spans="1:7">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" ht="40.5">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="7"/>
+      <c r="C23" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="E23" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" ht="54">
-      <c r="A24" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="7"/>
+    <row r="24" spans="1:7" ht="40.5">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" ht="54">
+      <c r="A25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="7"/>
@@ -2838,7 +2866,7 @@
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -2849,7 +2877,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -2860,20 +2888,20 @@
       <c r="C28" s="8"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="C29" s="8"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -2884,7 +2912,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -2892,10 +2920,12 @@
     <row r="31" spans="1:7">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="8"/>
+      <c r="C31" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -2906,7 +2936,7 @@
       <c r="C32" s="8"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
@@ -2917,22 +2947,18 @@
       <c r="C33" s="8"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
     </row>
-    <row r="34" spans="1:7" ht="40.5">
+    <row r="34" spans="1:7">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -2943,20 +2969,18 @@
       <c r="C35" s="8"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
     </row>
-    <row r="36" spans="1:7" ht="40.5">
+    <row r="36" spans="1:7">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>54</v>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -2964,79 +2988,77 @@
     <row r="37" spans="1:7" ht="40.5">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="8"/>
+      <c r="C37" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="D37" s="7" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
     </row>
-    <row r="38" spans="1:7" ht="27">
+    <row r="38" spans="1:7">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" ht="40.5">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7" t="s">
-        <v>13</v>
+      <c r="D39" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
     </row>
-    <row r="40" spans="1:7" ht="27">
+    <row r="40" spans="1:7" ht="40.5">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="8" t="s">
-        <v>69</v>
-      </c>
+      <c r="C40" s="8"/>
       <c r="D40" s="7" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" ht="27">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="7"/>
+      <c r="C41" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E41" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
     </row>
-    <row r="42" spans="1:7" ht="27">
+    <row r="42" spans="1:7">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="7"/>
       <c r="E42" s="7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -3045,91 +3067,97 @@
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D43" s="7"/>
+        <v>62</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="E43" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
     </row>
-    <row r="44" spans="1:7" ht="40.5">
-      <c r="A44" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+    <row r="44" spans="1:7">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+    </row>
+    <row r="45" spans="1:7" ht="27">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="7"/>
+      <c r="C45" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="E45" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F45" s="7"/>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" ht="27">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="8"/>
+      <c r="C46" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
+    <row r="47" spans="1:7" ht="40.5">
+      <c r="A47" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="7"/>
+      <c r="E48" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="G48" s="7"/>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
-      <c r="C49" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="C49" s="8"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -3140,7 +3168,7 @@
       <c r="C50" s="8"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -3150,8 +3178,8 @@
       <c r="B51" s="7"/>
       <c r="C51" s="8"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="7" t="s">
-        <v>19</v>
+      <c r="E51" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
@@ -3159,88 +3187,86 @@
     <row r="52" spans="1:7">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
-      <c r="C52" s="8"/>
+      <c r="C52" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
     </row>
-    <row r="53" spans="1:7" ht="40.5">
+    <row r="53" spans="1:7">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
-      <c r="C53" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="7"/>
       <c r="E53" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
     </row>
-    <row r="54" spans="1:7" ht="40.5">
+    <row r="54" spans="1:7">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>
-      <c r="D54" s="7" t="s">
-        <v>61</v>
-      </c>
+      <c r="D54" s="7"/>
       <c r="E54" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
     </row>
-    <row r="55" spans="1:7" ht="40.5">
+    <row r="55" spans="1:7">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="7" t="s">
-        <v>63</v>
-      </c>
+      <c r="D55" s="7"/>
       <c r="E55" s="7" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" ht="40.5">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="7"/>
+      <c r="C56" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="E56" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
     </row>
-    <row r="57" spans="1:7" ht="27">
+    <row r="57" spans="1:7" ht="40.5">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
-      <c r="C57" s="8" t="s">
-        <v>65</v>
-      </c>
+      <c r="C57" s="8"/>
       <c r="D57" s="7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" ht="40.5">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="8"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="12" t="s">
-        <v>54</v>
+      <c r="D58" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
@@ -3251,7 +3277,7 @@
       <c r="C59" s="8"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
@@ -3260,13 +3286,13 @@
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -3276,23 +3302,19 @@
       <c r="B61" s="7"/>
       <c r="C61" s="8"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="7" t="s">
-        <v>17</v>
+      <c r="E61" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
     </row>
-    <row r="62" spans="1:7" ht="27">
+    <row r="62" spans="1:7">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
-      <c r="C62" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="C62" s="8"/>
+      <c r="D62" s="7"/>
       <c r="E62" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -3301,11 +3323,13 @@
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D63" s="7"/>
+        <v>62</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="E63" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
@@ -3315,79 +3339,79 @@
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
       <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
+      <c r="E64" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
     </row>
     <row r="65" spans="1:7" ht="27">
-      <c r="A65" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G65" s="4"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
     </row>
     <row r="66" spans="1:7" ht="27">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
-      <c r="C66" s="8"/>
+      <c r="C66" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D66" s="7"/>
       <c r="E66" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>84</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F66" s="7"/>
       <c r="G66" s="7"/>
     </row>
-    <row r="67" spans="1:7" ht="27">
+    <row r="67" spans="1:7">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="8"/>
       <c r="D67" s="7"/>
-      <c r="E67" s="7" t="s">
-        <v>0</v>
-      </c>
+      <c r="E67" s="7"/>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
     </row>
     <row r="68" spans="1:7" ht="27">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-    </row>
-    <row r="69" spans="1:7" ht="108">
+      <c r="A68" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" spans="1:7" ht="27">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
-      <c r="C69" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>86</v>
-      </c>
+      <c r="C69" s="8"/>
+      <c r="D69" s="7"/>
       <c r="E69" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="F69" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="G69" s="7"/>
     </row>
     <row r="70" spans="1:7" ht="27">
@@ -3396,41 +3420,37 @@
       <c r="C70" s="8"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" ht="27">
-      <c r="A71" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G71" s="4"/>
-    </row>
-    <row r="72" spans="1:7" ht="27">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+    </row>
+    <row r="72" spans="1:7" ht="108">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="7"/>
+      <c r="C72" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="E72" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>84</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F72" s="7"/>
       <c r="G72" s="7"/>
     </row>
     <row r="73" spans="1:7" ht="27">
@@ -3439,37 +3459,41 @@
       <c r="C73" s="8"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
     </row>
     <row r="74" spans="1:7" ht="27">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-    </row>
-    <row r="75" spans="1:7" ht="108">
+      <c r="A74" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G74" s="4"/>
+    </row>
+    <row r="75" spans="1:7" ht="27">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
-      <c r="C75" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>86</v>
-      </c>
+      <c r="C75" s="8"/>
+      <c r="D75" s="7"/>
       <c r="E75" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F75" s="7"/>
+        <v>82</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="G75" s="7"/>
     </row>
     <row r="76" spans="1:7" ht="27">
@@ -3478,192 +3502,194 @@
       <c r="C76" s="8"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
     </row>
-    <row r="77" spans="1:7" ht="40.5">
-      <c r="A77" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="40.5">
+    <row r="77" spans="1:7" ht="27">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+    </row>
+    <row r="78" spans="1:7" ht="108">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D78" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="E78" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>95</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F78" s="7"/>
       <c r="G78" s="7"/>
     </row>
     <row r="79" spans="1:7" ht="27">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="8"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+    </row>
+    <row r="80" spans="1:7" ht="40.5">
+      <c r="A80" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="B80" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G79" s="7"/>
-    </row>
-    <row r="80" spans="1:7" ht="27">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G80" s="7"/>
-    </row>
-    <row r="81" spans="1:7" ht="27">
-      <c r="A81" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>99</v>
-      </c>
+    </row>
+    <row r="81" spans="1:7" ht="40.5">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G81" s="7"/>
     </row>
     <row r="82" spans="1:7" ht="27">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
+      <c r="C82" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="E82" s="7" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G82" s="7"/>
     </row>
     <row r="83" spans="1:7" ht="27">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
+      <c r="C83" s="8"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="G83" s="7"/>
     </row>
     <row r="84" spans="1:7" ht="27">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F84" s="7" t="s">
+      <c r="A84" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="27">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G84" s="7"/>
-    </row>
-    <row r="85" spans="1:7" ht="27">
-      <c r="A85" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G85" s="4"/>
+      <c r="F85" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" s="7"/>
     </row>
     <row r="86" spans="1:7" ht="27">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
-      <c r="C86" s="8"/>
+      <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="G86" s="7"/>
     </row>
     <row r="87" spans="1:7" ht="27">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
-      <c r="C87" s="8"/>
+      <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F87" s="7"/>
+        <v>94</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="G87" s="7"/>
     </row>
     <row r="88" spans="1:7" ht="27">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
+      <c r="A88" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G88" s="4"/>
     </row>
     <row r="89" spans="1:7" ht="27">
       <c r="A89" s="7"/>
@@ -3671,22 +3697,20 @@
       <c r="C89" s="8"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F89" s="7"/>
+        <v>98</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="G89" s="7"/>
     </row>
     <row r="90" spans="1:7" ht="27">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
-      <c r="C90" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="C90" s="8"/>
+      <c r="D90" s="7"/>
       <c r="E90" s="7" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
@@ -3694,88 +3718,92 @@
     <row r="91" spans="1:7" ht="27">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
-      <c r="C91" s="8"/>
+      <c r="C91" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="D91" s="7"/>
       <c r="E91" s="7" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
     </row>
-    <row r="92" spans="1:7" ht="40.5">
-      <c r="A92" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" s="4"/>
-    </row>
-    <row r="93" spans="1:7">
+    <row r="92" spans="1:7" ht="27">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+    </row>
+    <row r="93" spans="1:7" ht="27">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="7"/>
+      <c r="C93" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="E93" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="F93" s="7"/>
       <c r="G93" s="7"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" ht="27">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
     </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
+    <row r="95" spans="1:7" ht="40.5">
+      <c r="A95" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G95" s="4"/>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8"/>
       <c r="D96" s="7"/>
-      <c r="E96" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F96" s="7"/>
+      <c r="E96" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="G96" s="7"/>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
-      <c r="C97" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="C97" s="8"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
@@ -3786,7 +3814,7 @@
       <c r="C98" s="8"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7" t="s">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
@@ -3796,8 +3824,8 @@
       <c r="B99" s="7"/>
       <c r="C99" s="8"/>
       <c r="D99" s="7"/>
-      <c r="E99" s="7" t="s">
-        <v>4</v>
+      <c r="E99" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
@@ -3805,25 +3833,23 @@
     <row r="100" spans="1:7">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
-      <c r="C100" s="8"/>
+      <c r="C100" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="D100" s="7"/>
       <c r="E100" s="7" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
     </row>
-    <row r="101" spans="1:7" ht="67.5">
+    <row r="101" spans="1:7">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="C101" s="8"/>
+      <c r="D101" s="7"/>
       <c r="E101" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
@@ -3833,21 +3859,19 @@
       <c r="B102" s="7"/>
       <c r="C102" s="8"/>
       <c r="D102" s="7"/>
-      <c r="E102" s="12" t="s">
-        <v>110</v>
+      <c r="E102" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
     </row>
-    <row r="103" spans="1:7" ht="67.5">
+    <row r="103" spans="1:7">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="7" t="s">
-        <v>112</v>
-      </c>
+      <c r="D103" s="7"/>
       <c r="E103" s="7" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
@@ -3855,12 +3879,14 @@
     <row r="104" spans="1:7" ht="67.5">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
-      <c r="C104" s="8"/>
+      <c r="C104" s="8" t="s">
+        <v>78</v>
+      </c>
       <c r="D104" s="7" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
@@ -3870,114 +3896,116 @@
       <c r="B105" s="7"/>
       <c r="C105" s="8"/>
       <c r="D105" s="7"/>
-      <c r="E105" s="7" t="s">
-        <v>30</v>
+      <c r="E105" s="12" t="s">
+        <v>102</v>
       </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
     </row>
-    <row r="106" spans="1:7" ht="27">
+    <row r="106" spans="1:7" ht="67.5">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
-      <c r="C106" s="8" t="s">
-        <v>72</v>
-      </c>
+      <c r="C106" s="8"/>
       <c r="D106" s="7" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
     </row>
-    <row r="107" spans="1:7" ht="40.5">
+    <row r="107" spans="1:7" ht="67.5">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
-      <c r="C107" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D107" s="7"/>
-      <c r="E107" s="10" t="s">
-        <v>115</v>
+      <c r="C107" s="8"/>
+      <c r="D107" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="F107" s="7"/>
-      <c r="G107" s="10"/>
-    </row>
-    <row r="108" spans="1:7" ht="40.5">
-      <c r="A108" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G108" s="4"/>
-    </row>
-    <row r="109" spans="1:7">
+      <c r="G107" s="7"/>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+    </row>
+    <row r="109" spans="1:7" ht="27">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="7"/>
+      <c r="C109" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="E109" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F109" s="7"/>
       <c r="G109" s="7"/>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" ht="40.5">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
-      <c r="C110" s="8"/>
+      <c r="C110" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D110" s="7"/>
-      <c r="E110" s="7" t="s">
-        <v>119</v>
+      <c r="E110" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="7"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
+      <c r="G110" s="10"/>
+    </row>
+    <row r="111" spans="1:7" ht="40.5">
+      <c r="A111" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G111" s="4"/>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="8"/>
       <c r="D112" s="7"/>
-      <c r="E112" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="F112" s="7"/>
+      <c r="E112" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="G112" s="7"/>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
-      <c r="C113" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="C113" s="8"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
@@ -3988,7 +4016,7 @@
       <c r="C114" s="8"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -3998,8 +4026,8 @@
       <c r="B115" s="7"/>
       <c r="C115" s="8"/>
       <c r="D115" s="7"/>
-      <c r="E115" s="7" t="s">
-        <v>119</v>
+      <c r="E115" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
@@ -4007,25 +4035,23 @@
     <row r="116" spans="1:7">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
-      <c r="C116" s="8"/>
+      <c r="C116" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="D116" s="7"/>
       <c r="E116" s="7" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
     </row>
-    <row r="117" spans="1:7" ht="67.5">
+    <row r="117" spans="1:7">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
-      <c r="C117" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="C117" s="8"/>
+      <c r="D117" s="7"/>
       <c r="E117" s="7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
@@ -4035,21 +4061,19 @@
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
       <c r="D118" s="7"/>
-      <c r="E118" s="12" t="s">
-        <v>110</v>
+      <c r="E118" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
     </row>
-    <row r="119" spans="1:7" ht="67.5">
+    <row r="119" spans="1:7">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
-      <c r="D119" s="7" t="s">
-        <v>112</v>
-      </c>
+      <c r="D119" s="7"/>
       <c r="E119" s="7" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
@@ -4057,12 +4081,14 @@
     <row r="120" spans="1:7" ht="67.5">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
-      <c r="C120" s="8"/>
+      <c r="C120" s="8" t="s">
+        <v>78</v>
+      </c>
       <c r="D120" s="7" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
@@ -4072,91 +4098,89 @@
       <c r="B121" s="7"/>
       <c r="C121" s="8"/>
       <c r="D121" s="7"/>
-      <c r="E121" s="7" t="s">
-        <v>30</v>
+      <c r="E121" s="12" t="s">
+        <v>102</v>
       </c>
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
     </row>
-    <row r="122" spans="1:7" ht="27">
+    <row r="122" spans="1:7" ht="67.5">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
-      <c r="C122" s="8" t="s">
-        <v>72</v>
-      </c>
+      <c r="C122" s="8"/>
       <c r="D122" s="7" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="F122" s="7"/>
       <c r="G122" s="7"/>
     </row>
-    <row r="123" spans="1:7" ht="40.5">
+    <row r="123" spans="1:7" ht="67.5">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
-      <c r="C123" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D123" s="7"/>
-      <c r="E123" s="10" t="s">
-        <v>115</v>
+      <c r="C123" s="8"/>
+      <c r="D123" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="F123" s="7"/>
-      <c r="G123" s="10"/>
-    </row>
-    <row r="124" spans="1:7" ht="40.5">
-      <c r="A124" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C124" s="5"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
-      <c r="F124" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G124" s="4"/>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="G123" s="7"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="7"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F124" s="7"/>
+      <c r="G124" s="7"/>
+    </row>
+    <row r="125" spans="1:7" ht="27">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
-      <c r="C125" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="C125" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F125" s="7"/>
       <c r="G125" s="7"/>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" ht="40.5">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
-      <c r="C126" s="8"/>
+      <c r="C126" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
+      <c r="E126" s="10" t="s">
+        <v>107</v>
+      </c>
       <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
+      <c r="G126" s="10"/>
     </row>
     <row r="127" spans="1:7" ht="40.5">
       <c r="A127" s="4" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C127" s="5"/>
       <c r="D127" s="4"/>
-      <c r="E127" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="E127" s="4"/>
       <c r="F127" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G127" s="4"/>
     </row>
@@ -4164,14 +4188,12 @@
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="D128" s="7"/>
-      <c r="E128" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="E128" s="7"/>
       <c r="F128" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G128" s="7"/>
     </row>
@@ -4184,28 +4206,36 @@
       <c r="F129" s="7"/>
       <c r="G129" s="7"/>
     </row>
-    <row r="130" spans="1:7" ht="67.5">
+    <row r="130" spans="1:7" ht="40.5">
       <c r="A130" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C130" s="14" t="s">
-        <v>142</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C130" s="5"/>
       <c r="D130" s="4"/>
-      <c r="E130" s="4"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="14"/>
+      <c r="E130" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G130" s="4"/>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
-      <c r="C131" s="8"/>
+      <c r="C131" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
+      <c r="E131" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="G131" s="7"/>
     </row>
     <row r="132" spans="1:7">
@@ -4217,39 +4247,27 @@
       <c r="F132" s="7"/>
       <c r="G132" s="7"/>
     </row>
-    <row r="133" spans="1:7" ht="54">
+    <row r="133" spans="1:7" ht="67.5">
       <c r="A133" s="4" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="27">
+        <v>45</v>
+      </c>
+      <c r="C133" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+      <c r="G133" s="14"/>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="8"/>
-      <c r="D134" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>130</v>
-      </c>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
     </row>
@@ -4258,38 +4276,44 @@
       <c r="B135" s="7"/>
       <c r="C135" s="8"/>
       <c r="D135" s="7"/>
-      <c r="E135" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="E135" s="7"/>
       <c r="F135" s="7"/>
       <c r="G135" s="7"/>
     </row>
-    <row r="136" spans="1:7">
-      <c r="A136" s="7"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
-    </row>
-    <row r="137" spans="1:7" ht="40.5">
+    <row r="136" spans="1:7" ht="54">
+      <c r="A136" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="27">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
-      <c r="C137" s="8" t="s">
-        <v>131</v>
-      </c>
+      <c r="C137" s="8"/>
       <c r="D137" s="7" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>132</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F137" s="7"/>
       <c r="G137" s="7"/>
     </row>
     <row r="138" spans="1:7">
@@ -4298,64 +4322,64 @@
       <c r="C138" s="8"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F138" s="7"/>
       <c r="G138" s="7"/>
     </row>
-    <row r="139" spans="1:7" ht="40.5">
-      <c r="A139" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C139" s="5"/>
-      <c r="D139" s="4"/>
-      <c r="E139" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F139" s="4"/>
-      <c r="G139" s="4"/>
-    </row>
-    <row r="140" spans="1:7" ht="27">
+    <row r="139" spans="1:7">
+      <c r="A139" s="7"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
+    </row>
+    <row r="140" spans="1:7" ht="40.5">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
+      <c r="C140" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="E140" s="7" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="G140" s="7"/>
     </row>
-    <row r="141" spans="1:7" ht="67.5">
+    <row r="141" spans="1:7">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
-      <c r="C141" s="7"/>
+      <c r="C141" s="8"/>
       <c r="D141" s="7"/>
-      <c r="E141" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="E141" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F141" s="7"/>
       <c r="G141" s="7"/>
     </row>
-    <row r="142" spans="1:7" ht="67.5">
-      <c r="A142" s="7"/>
-      <c r="B142" s="7"/>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="G142" s="7"/>
+    <row r="142" spans="1:7" ht="40.5">
+      <c r="A142" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C142" s="5"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
     </row>
     <row r="143" spans="1:7" ht="27">
       <c r="A143" s="7"/>
@@ -4363,93 +4387,93 @@
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G143" s="7"/>
     </row>
-    <row r="144" spans="1:7" ht="40.5">
-      <c r="A144" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C144" s="5" t="s">
+    <row r="144" spans="1:7" ht="67.5">
+      <c r="A144" s="7"/>
+      <c r="B144" s="7"/>
+      <c r="C144" s="7"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F144" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D144" s="4"/>
-      <c r="E144" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G144" s="4"/>
-    </row>
-    <row r="145" spans="1:7" ht="27">
+      <c r="G144" s="7"/>
+    </row>
+    <row r="145" spans="1:7" ht="67.5">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
-      <c r="C145" s="8"/>
+      <c r="C145" s="7"/>
       <c r="D145" s="7"/>
-      <c r="E145" s="7" t="s">
-        <v>150</v>
+      <c r="E145" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="G145" s="7"/>
     </row>
     <row r="146" spans="1:7" ht="27">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="C146" s="7"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="F146" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>128</v>
+      </c>
       <c r="G146" s="7"/>
     </row>
-    <row r="147" spans="1:7" ht="27">
-      <c r="A147" s="7"/>
-      <c r="B147" s="7"/>
-      <c r="C147" s="8"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-    </row>
-    <row r="148" spans="1:7" ht="67.5">
+    <row r="147" spans="1:7" ht="40.5">
+      <c r="A147" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G147" s="4"/>
+    </row>
+    <row r="148" spans="1:7" ht="27">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
-      <c r="C148" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D148" s="7" t="s">
-        <v>111</v>
-      </c>
+      <c r="C148" s="8"/>
+      <c r="D148" s="7"/>
       <c r="E148" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F148" s="7"/>
+        <v>142</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="G148" s="7"/>
     </row>
-    <row r="149" spans="1:7" ht="67.5">
+    <row r="149" spans="1:7" ht="27">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="8"/>
-      <c r="D149" s="7" t="s">
-        <v>112</v>
-      </c>
+      <c r="C149" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D149" s="7"/>
       <c r="E149" s="7" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
@@ -4457,70 +4481,109 @@
     <row r="150" spans="1:7" ht="27">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
-      <c r="C150" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D150" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="C150" s="8"/>
+      <c r="D150" s="7"/>
       <c r="E150" s="7" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F150" s="7"/>
       <c r="G150" s="7"/>
     </row>
-    <row r="151" spans="1:7" ht="40.5">
+    <row r="151" spans="1:7" ht="67.5">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D151" s="7"/>
-      <c r="E151" s="10" t="s">
-        <v>156</v>
+        <v>78</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="F151" s="7"/>
-      <c r="G151" s="10"/>
-    </row>
-    <row r="152" spans="1:7" ht="40.5">
-      <c r="A152" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C152" s="5"/>
-      <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
-      <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="G151" s="7"/>
+    </row>
+    <row r="152" spans="1:7" ht="67.5">
+      <c r="A152" s="7"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
+    </row>
+    <row r="153" spans="1:7" ht="27">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
-      <c r="C153" s="8"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
+      <c r="C153" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>147</v>
+      </c>
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" ht="40.5">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
-      <c r="C154" s="8"/>
+      <c r="C154" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
+      <c r="E154" s="10" t="s">
+        <v>148</v>
+      </c>
       <c r="F154" s="7"/>
-      <c r="G154" s="7"/>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="D155" s="9"/>
-      <c r="E155" s="9"/>
-      <c r="F155" s="9"/>
-      <c r="G155" s="9"/>
+      <c r="G154" s="10"/>
+    </row>
+    <row r="155" spans="1:7" ht="40.5">
+      <c r="A155" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C155" s="5"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="7"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="7"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="D158" s="9"/>
+      <c r="E158" s="9"/>
+      <c r="F158" s="9"/>
+      <c r="G158" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G143"/>
+  <autoFilter ref="A1:G146"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
